--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -729,6 +729,12 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
+  </si>
+  <si>
+    <t>956: source value from PTF - PRINCIPAL DIAGNOSIS (#45-79)</t>
+  </si>
+  <si>
+    <t>Inpat.Inpatient.PrincipalDiagnosisICDIEN</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -756,12 +762,6 @@
   </si>
   <si>
     <t>246090004</t>
-  </si>
-  <si>
-    <t>956: source value from PTF - PRINCIPAL DIAGNOSIS (#45-79)</t>
-  </si>
-  <si>
-    <t>Inpat.Inpatient.PrincipalDiagnosisICDIEN</t>
   </si>
   <si>
     <t>Condition.bodySite</t>
@@ -1530,14 +1530,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="68.20703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="222.1015625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1776,22 +1776,22 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>81</v>
@@ -2413,13 +2413,13 @@
         <v>81</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>81</v>
@@ -2539,13 +2539,13 @@
         <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>81</v>
@@ -2917,13 +2917,13 @@
         <v>81</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP11" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>81</v>
@@ -3036,25 +3036,25 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AN12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AQ12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ12" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR12" t="s" s="2">
         <v>81</v>
@@ -3160,25 +3160,25 @@
         <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AO13" t="s" s="2">
+      <c r="AQ13" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ13" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>81</v>
@@ -3284,28 +3284,28 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AR14" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR14" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3411,22 +3411,22 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>81</v>
@@ -3537,22 +3537,22 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>81</v>
@@ -3665,22 +3665,22 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>81</v>
@@ -3791,25 +3791,25 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AR18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR18" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4043,25 +4043,25 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AO20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4166,25 +4166,25 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>81</v>
@@ -4292,25 +4292,25 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>81</v>
@@ -4418,25 +4418,25 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4553,16 +4553,16 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -4674,19 +4674,19 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>81</v>
@@ -4801,16 +4801,16 @@
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>81</v>
@@ -4922,19 +4922,19 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>81</v>
@@ -5049,13 +5049,13 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>81</v>
@@ -5173,13 +5173,13 @@
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
@@ -5299,13 +5299,13 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>81</v>
@@ -5427,13 +5427,13 @@
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -5545,19 +5545,19 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AN32" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AP32" t="s" s="2">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>81</v>
@@ -5675,13 +5675,13 @@
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -5799,13 +5799,13 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
@@ -5925,13 +5925,13 @@
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6049,13 +6049,13 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6175,13 +6175,13 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6303,13 +6303,13 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
@@ -6418,25 +6418,25 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -6551,16 +6551,16 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -6666,22 +6666,22 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PTF (#45) to us-core-condition-problems-health-concerns</t>
+    <t>This StructureDefinition contains the maps for VistA file PTF (45) to us-core-condition-problems-health-concerns</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -731,7 +731,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
   </si>
   <si>
-    <t>956: source value from PTF - PRINCIPAL DIAGNOSIS (#45-79)</t>
+    <t>956: source value from PTF - PRINCIPAL DIAGNOSIS (45-79)</t>
   </si>
   <si>
     <t>Inpat.Inpatient.PrincipalDiagnosisICDIEN</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="369">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -628,6 +628,13 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="problem-list-item"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -636,6 +643,9 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
+  </si>
+  <si>
+    <t>956-1: fixed value = #problem-list-item</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -3356,7 +3366,7 @@
         <v>81</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>81</v>
@@ -3371,19 +3381,19 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y15" t="s" s="2">
         <v>193</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
@@ -3408,7 +3418,7 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
@@ -3417,16 +3427,16 @@
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>81</v>
@@ -3434,13 +3444,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>81</v>
@@ -3465,7 +3475,7 @@
         <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>193</v>
@@ -3501,7 +3511,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3543,16 +3553,16 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>81</v>
@@ -3560,13 +3570,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
@@ -3591,7 +3601,7 @@
         <v>169</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>193</v>
@@ -3608,7 +3618,7 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>81</v>
@@ -3623,13 +3633,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y17" t="s" s="2">
         <v>193</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -3671,16 +3681,16 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>81</v>
@@ -3688,10 +3698,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3717,13 +3727,13 @@
         <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3752,28 +3762,28 @@
         <v>117</v>
       </c>
       <c r="Y18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -3797,31 +3807,31 @@
         <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3843,14 +3853,14 @@
         <v>169</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3875,13 +3885,13 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>81</v>
@@ -3899,7 +3909,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -3914,36 +3924,36 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3969,13 +3979,13 @@
         <v>169</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4001,13 +4011,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4025,7 +4035,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4049,31 +4059,31 @@
         <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4092,17 +4102,17 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4151,7 +4161,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>93</v>
@@ -4172,19 +4182,19 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>81</v>
@@ -4192,10 +4202,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4218,16 +4228,16 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4277,7 +4287,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4298,19 +4308,19 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>81</v>
@@ -4318,10 +4328,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4344,16 +4354,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4403,7 +4413,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4424,19 +4434,19 @@
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4444,10 +4454,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4470,16 +4480,16 @@
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4529,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4538,7 +4548,7 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>105</v>
@@ -4559,10 +4569,10 @@
         <v>81</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -4570,10 +4580,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4596,13 +4606,13 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4653,7 +4663,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4680,13 +4690,13 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>81</v>
@@ -4694,10 +4704,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4720,13 +4730,13 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4777,7 +4787,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -4807,10 +4817,10 @@
         <v>81</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>81</v>
@@ -4818,10 +4828,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4844,13 +4854,13 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4901,7 +4911,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -4928,13 +4938,13 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>81</v>
@@ -4942,10 +4952,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4968,13 +4978,13 @@
         <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5025,7 +5035,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5037,7 +5047,7 @@
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5055,7 +5065,7 @@
         <v>81</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>81</v>
@@ -5066,10 +5076,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5092,13 +5102,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5149,7 +5159,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5179,7 +5189,7 @@
         <v>81</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
@@ -5190,10 +5200,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5219,10 +5229,10 @@
         <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>156</v>
@@ -5275,7 +5285,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5305,7 +5315,7 @@
         <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>81</v>
@@ -5316,14 +5326,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5345,10 +5355,10 @@
         <v>138</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>156</v>
@@ -5403,7 +5413,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5444,10 +5454,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5473,10 +5483,10 @@
         <v>169</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5503,13 +5513,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -5527,7 +5537,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5536,7 +5546,7 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>105</v>
@@ -5551,13 +5561,13 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>178</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>81</v>
@@ -5568,10 +5578,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5594,13 +5604,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5651,7 +5661,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5660,7 +5670,7 @@
         <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
@@ -5681,7 +5691,7 @@
         <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -5692,10 +5702,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5721,10 +5731,10 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5751,13 +5761,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -5775,7 +5785,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -5805,7 +5815,7 @@
         <v>81</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
@@ -5816,10 +5826,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5842,16 +5852,16 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5901,7 +5911,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -5913,7 +5923,7 @@
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -5931,7 +5941,7 @@
         <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -5942,10 +5952,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5968,13 +5978,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6025,7 +6035,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6055,7 +6065,7 @@
         <v>81</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6066,10 +6076,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6095,10 +6105,10 @@
         <v>138</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>156</v>
@@ -6151,7 +6161,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6181,7 +6191,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6192,14 +6202,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6221,10 +6231,10 @@
         <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>156</v>
@@ -6279,7 +6289,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6320,10 +6330,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6349,10 +6359,10 @@
         <v>169</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6379,13 +6389,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6403,7 +6413,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6412,7 +6422,7 @@
         <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6424,19 +6434,19 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -6444,10 +6454,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6470,13 +6480,13 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6527,7 +6537,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6536,7 +6546,7 @@
         <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6557,10 +6567,10 @@
         <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -6568,10 +6578,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6594,13 +6604,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6651,7 +6661,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6672,16 +6682,16 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -628,48 +628,49 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Condition.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>problem-list-item | health-concern</t>
+  </si>
+  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/condition-category"/&gt;
     &lt;code value="problem-list-item"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>956-1: fixed value = #problem-list-item</t>
-  </si>
-  <si>
-    <t>&lt; 404684003 |Clinical finding|</t>
-  </si>
-  <si>
-    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Condition.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>problem-list-item | health-concern</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-problem-or-health-concern</t>
+  </si>
+  <si>
+    <t>956-1: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#problem-list-item</t>
   </si>
   <si>
     <t>Condition.category:sdoh</t>
@@ -1540,7 +1541,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="91.4375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -3366,34 +3367,34 @@
         <v>81</v>
       </c>
       <c r="S15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="Y15" t="s" s="2">
         <v>193</v>
       </c>
       <c r="Z15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
@@ -3418,25 +3419,25 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>81</v>
@@ -3444,13 +3445,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>81</v>
@@ -3475,7 +3476,7 @@
         <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>193</v>
@@ -3492,7 +3493,7 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>81</v>
@@ -3511,7 +3512,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3544,7 +3545,7 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>81</v>
@@ -3553,16 +3554,16 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>81</v>
@@ -3633,13 +3634,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
         <v>193</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -3681,16 +3682,16 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>81</v>
@@ -3885,7 +3886,7 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y19" t="s" s="2">
         <v>227</v>
@@ -6437,7 +6438,7 @@
         <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -628,49 +628,48 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>&lt; 404684003 |Clinical finding|</t>
-  </si>
-  <si>
-    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Condition.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>problem-list-item | health-concern</t>
-  </si>
-  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/condition-category"/&gt;
     &lt;code value="problem-list-item"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>956-1: fixed value = #problem-list-item</t>
+  </si>
+  <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Condition.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>problem-list-item | health-concern</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-problem-or-health-concern</t>
-  </si>
-  <si>
-    <t>956-1: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#problem-list-item</t>
   </si>
   <si>
     <t>Condition.category:sdoh</t>
@@ -1541,7 +1540,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="91.4375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -3367,7 +3366,7 @@
         <v>81</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>81</v>
@@ -3382,19 +3381,19 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y15" t="s" s="2">
         <v>193</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
@@ -3419,7 +3418,7 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
@@ -3428,16 +3427,16 @@
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>81</v>
@@ -3445,13 +3444,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>81</v>
@@ -3476,7 +3475,7 @@
         <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>193</v>
@@ -3493,7 +3492,7 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>81</v>
@@ -3512,7 +3511,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3545,7 +3544,7 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>81</v>
@@ -3554,16 +3553,16 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>81</v>
@@ -3634,13 +3633,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y17" t="s" s="2">
         <v>193</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -3682,16 +3681,16 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>81</v>
@@ -3886,7 +3885,7 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y19" t="s" s="2">
         <v>227</v>
@@ -6438,7 +6437,7 @@
         <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,6 +630,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/condition-category"/&gt;
     &lt;code value="problem-list-item"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -645,7 +646,7 @@
 </t>
   </si>
   <si>
-    <t>956-1: fixed value = #problem-list-item</t>
+    <t>956-1: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#problem-list-item</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -1540,7 +1541,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="91.4375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,7 +631,7 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://terminology.hl7.org/CodeSystem/condition-category"/&gt;
-    &lt;code value="problem-list-item"/&gt;
+    &lt;code value="encounter-diagnosis"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -646,7 +646,7 @@
 </t>
   </si>
   <si>
-    <t>956-1: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#problem-list-item</t>
+    <t>956-1: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#encounter-diagnosis</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -1541,7 +1541,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="91.4375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="94.32421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$41</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="371">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -746,6 +749,9 @@
   </si>
   <si>
     <t>Inpat.Inpatient.PrincipalDiagnosisICDIEN</t>
+  </si>
+  <si>
+    <t>Diagnosis.Diagnosis,Diagnosis.DiagnosisType</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1503,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR41"/>
+  <dimension ref="A1:AS41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.88671875" customWidth="true" bestFit="true"/>
@@ -1543,12 +1549,13 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="94.32421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="68.20703125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="222.1015625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1684,6 +1691,9 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
+      <c r="AS1" t="s" s="1">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1694,106 +1704,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>89</v>
@@ -1805,1379 +1815,1412 @@
         <v>91</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AR2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS2" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS3" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS4" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS5" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS6" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="AR7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS7" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AR8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS8" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS9" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS10" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS11" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>81</v>
+        <v>168</v>
+      </c>
+      <c r="AS12" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>177</v>
@@ -3192,119 +3235,122 @@
         <v>180</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
+      </c>
+      <c r="AS13" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>188</v>
@@ -3313,122 +3359,125 @@
         <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
+      </c>
+      <c r="AS14" t="s" s="2">
+        <v>191</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>201</v>
@@ -3440,121 +3489,124 @@
         <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
+      </c>
+      <c r="AS15" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>201</v>
@@ -3566,123 +3618,126 @@
         <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
+      </c>
+      <c r="AS16" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>201</v>
@@ -3694,121 +3749,124 @@
         <v>203</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
+      </c>
+      <c r="AS17" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>218</v>
@@ -3821,2888 +3879,2960 @@
       </c>
       <c r="AR18" t="s" s="2">
         <v>221</v>
+      </c>
+      <c r="AS18" t="s" s="2">
+        <v>222</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="AS19" t="s" s="2">
+        <v>238</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
+      </c>
+      <c r="AS20" t="s" s="2">
+        <v>248</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>81</v>
+        <v>258</v>
+      </c>
+      <c r="AS21" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
+      </c>
+      <c r="AS22" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>81</v>
+        <v>283</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>178</v>
+        <v>330</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI33" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>200</v>
+        <v>357</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>368</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR41">
+  <autoFilter ref="A1:AS41">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PTF (45) to us-core-condition-problems-health-concerns</t>
+    <t>This StructureDefinition contains the maps for VistA file PTF (45) to us-core-condition-problems-health-concerns.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$43</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="383">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,6 +493,9 @@
 </t>
   </si>
   <si>
+    <t>2145: target not supported</t>
+  </si>
+  <si>
     <t>Condition.modifierExtension</t>
   </si>
   <si>
@@ -570,6 +573,9 @@
 con-4con-5</t>
   </si>
   <si>
+    <t>2146: target not supported</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -604,6 +610,9 @@
   <si>
     <t>con-3
 con-5</t>
+  </si>
+  <si>
+    <t>2147: target not supported</t>
   </si>
   <si>
     <t>&lt; 410514004 |Finding context value|</t>
@@ -831,6 +840,9 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
+    <t>2148: target not supported</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -887,6 +899,10 @@
     <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -897,6 +913,19 @@
   </si>
   <si>
     <t>FiveWs.init</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetDateTime</t>
+  </si>
+  <si>
+    <t>onsetDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>2149: target not supported</t>
   </si>
   <si>
     <t>Condition.abatement[x]</t>
@@ -921,17 +950,25 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>2150: target not supported</t>
+  </si>
+  <si>
     <t>Condition.recordedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
     <t>Date record was first recorded</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
+  </si>
+  <si>
+    <t>2151: target not supported</t>
   </si>
   <si>
     <t>REL-11</t>
@@ -1509,12 +1546,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS41"/>
+  <dimension ref="A1:AS43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.3515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.01953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2825,7 +2862,7 @@
         <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>82</v>
@@ -2854,14 +2891,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2883,16 +2920,16 @@
         <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -2941,7 +2978,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
@@ -2985,10 +3022,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3011,19 +3048,19 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3072,7 +3109,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -3096,7 +3133,7 @@
         <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3105,10 +3142,10 @@
         <v>82</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AS12" t="s" s="2">
         <v>82</v>
@@ -3116,10 +3153,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3142,16 +3179,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3177,11 +3214,11 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>82</v>
@@ -3199,7 +3236,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -3208,13 +3245,13 @@
         <v>94</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
@@ -3223,19 +3260,19 @@
         <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS13" t="s" s="2">
         <v>82</v>
@@ -3243,10 +3280,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3269,16 +3306,16 @@
         <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3304,11 +3341,11 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3326,7 +3363,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
@@ -3335,13 +3372,13 @@
         <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>82</v>
@@ -3350,30 +3387,30 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS14" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3396,16 +3433,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3416,7 +3453,7 @@
         <v>82</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>82</v>
@@ -3431,19 +3468,19 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
@@ -3453,7 +3490,7 @@
         <v>143</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -3468,7 +3505,7 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>82</v>
@@ -3480,16 +3517,16 @@
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AS15" t="s" s="2">
         <v>82</v>
@@ -3497,13 +3534,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>82</v>
@@ -3525,16 +3562,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3560,11 +3597,11 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3582,7 +3619,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -3609,16 +3646,16 @@
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>82</v>
@@ -3626,13 +3663,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>82</v>
@@ -3654,16 +3691,16 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3674,7 +3711,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -3689,13 +3726,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="Z17" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3713,7 +3750,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -3740,16 +3777,16 @@
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AS17" t="s" s="2">
         <v>82</v>
@@ -3757,10 +3794,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3783,16 +3820,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3821,10 +3858,10 @@
         <v>118</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -3842,7 +3879,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
@@ -3869,31 +3906,31 @@
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AS18" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3912,17 +3949,17 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -3947,13 +3984,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -3971,7 +4008,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -3986,39 +4023,39 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AS19" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4041,16 +4078,16 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4076,13 +4113,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4100,7 +4137,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4127,31 +4164,31 @@
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS20" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4170,17 +4207,17 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4229,7 +4266,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>94</v>
@@ -4244,7 +4281,7 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
@@ -4253,19 +4290,19 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4273,10 +4310,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4299,16 +4336,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4358,7 +4395,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4382,19 +4419,19 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>82</v>
@@ -4402,10 +4439,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4428,16 +4465,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4475,19 +4512,17 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4511,19 +4546,19 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -4531,12 +4566,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4554,19 +4591,19 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4616,7 +4653,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -4625,13 +4662,13 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -4640,19 +4677,19 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -4660,10 +4697,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4683,18 +4720,20 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4731,19 +4770,17 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -4752,7 +4789,7 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -4773,13 +4810,13 @@
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AS25" t="s" s="2">
         <v>82</v>
@@ -4787,12 +4824,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4804,24 +4843,26 @@
         <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4870,7 +4911,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -4879,13 +4920,13 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
@@ -4903,10 +4944,10 @@
         <v>82</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AS26" t="s" s="2">
         <v>82</v>
@@ -4914,10 +4955,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4931,7 +4972,7 @@
         <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -4940,13 +4981,13 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4997,7 +5038,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5012,7 +5053,7 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5055,7 +5096,7 @@
         <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5064,7 +5105,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>304</v>
@@ -5130,37 +5171,37 @@
         <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
+      <c r="AR28" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS28" t="s" s="2">
         <v>82</v>
@@ -5191,16 +5232,16 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5251,7 +5292,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5263,7 +5304,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5281,13 +5322,13 @@
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AQ29" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS29" t="s" s="2">
         <v>82</v>
@@ -5302,7 +5343,7 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5321,17 +5362,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>139</v>
+        <v>316</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5380,7 +5419,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5392,7 +5431,7 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>145</v>
+        <v>319</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5413,7 +5452,7 @@
         <v>82</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>82</v>
@@ -5424,46 +5463,42 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>139</v>
+        <v>322</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5511,19 +5546,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5544,7 +5579,7 @@
         <v>82</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>137</v>
+        <v>326</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>82</v>
@@ -5555,21 +5590,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5581,15 +5616,17 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5614,13 +5651,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5638,19 +5675,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5665,13 +5702,13 @@
         <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>236</v>
+        <v>326</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -5689,7 +5726,7 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5702,13 +5739,13 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>332</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>333</v>
@@ -5716,8 +5753,12 @@
       <c r="M33" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="N33" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5765,7 +5806,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -5774,10 +5815,10 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5798,7 +5839,7 @@
         <v>82</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>335</v>
+        <v>137</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -5835,7 +5876,7 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>337</v>
@@ -5868,7 +5909,7 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Y34" t="s" s="2">
         <v>339</v>
@@ -5901,7 +5942,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -5919,13 +5960,13 @@
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>341</v>
+        <v>239</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -5936,10 +5977,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5962,17 +6003,15 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6021,7 +6060,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6030,10 +6069,10 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>346</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6091,13 +6130,13 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>310</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6124,13 +6163,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6148,7 +6187,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6160,7 +6199,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6181,7 +6220,7 @@
         <v>82</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6192,14 +6231,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6218,16 +6257,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>139</v>
+        <v>316</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>157</v>
+        <v>357</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6277,7 +6316,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6289,7 +6328,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>145</v>
+        <v>358</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6310,7 +6349,7 @@
         <v>82</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6321,46 +6360,42 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>322</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6408,19 +6443,19 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6441,7 +6476,7 @@
         <v>82</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>137</v>
+        <v>326</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
@@ -6452,14 +6487,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6475,18 +6510,20 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6511,13 +6548,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6535,7 +6572,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -6544,10 +6581,10 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6559,19 +6596,19 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>82</v>
@@ -6579,14 +6616,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6599,22 +6636,26 @@
         <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6662,7 +6703,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -6671,10 +6712,10 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6695,10 +6736,10 @@
         <v>82</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>335</v>
+        <v>137</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>82</v>
@@ -6706,10 +6747,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6729,16 +6770,16 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6765,13 +6806,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6789,7 +6830,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -6798,7 +6839,7 @@
         <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6813,26 +6854,280 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>370</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AS41" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AR42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AR43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS43" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS41">
+  <autoFilter ref="A1:AS43">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6842,7 +7137,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI40">
+  <conditionalFormatting sqref="A2:AI42">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -754,7 +754,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
   </si>
   <si>
-    <t>956: source value from PTF - PRINCIPAL DIAGNOSIS (45-79)</t>
+    <t>956: source value based on PTF - PRINCIPAL DIAGNOSIS (45-79)</t>
   </si>
   <si>
     <t>Inpat.Inpatient.PrincipalDiagnosisICDIEN</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$47</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="401">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,6 +493,80 @@
 </t>
   </si>
   <si>
+    <t>Condition.extension:assertedDate.id</t>
+  </si>
+  <si>
+    <t>Condition.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.url</t>
+  </si>
+  <si>
+    <t>Condition.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/condition-assertedDate</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
     <t>2145: target not supported</t>
   </si>
   <si>
@@ -638,6 +712,37 @@
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Condition.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>problem-list-item | health-concern</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -648,41 +753,10 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-problem-or-health-concern</t>
   </si>
   <si>
     <t>956-1: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#encounter-diagnosis</t>
-  </si>
-  <si>
-    <t>&lt; 404684003 |Clinical finding|</t>
-  </si>
-  <si>
-    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Condition.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>problem-list-item | health-concern</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-problem-or-health-concern</t>
   </si>
   <si>
     <t>Condition.category:sdoh</t>
@@ -921,10 +995,6 @@
     <t>onsetDateTime</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
     <t>2149: target not supported</t>
   </si>
   <si>
@@ -1044,18 +1114,6 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Condition.stage.extension</t>
   </si>
   <si>
@@ -1063,9 +1121,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Condition.stage.modifierExtension</t>
@@ -1546,7 +1601,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS43"/>
+  <dimension ref="A1:AS47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
@@ -1577,7 +1632,7 @@
     <col min="26" max="26" width="65.6796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
@@ -2862,7 +2917,7 @@
         <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>82</v>
@@ -2891,46 +2946,42 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>154</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -2978,19 +3029,19 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3011,7 +3062,7 @@
         <v>82</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>82</v>
@@ -3022,10 +3073,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3036,7 +3087,7 @@
         <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3045,23 +3096,19 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3097,19 +3144,19 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -3121,7 +3168,7 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
@@ -3133,7 +3180,7 @@
         <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3142,10 +3189,10 @@
         <v>82</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AS12" t="s" s="2">
         <v>82</v>
@@ -3153,10 +3200,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3164,31 +3211,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3196,7 +3243,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>82</v>
@@ -3214,11 +3261,13 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>82</v>
@@ -3236,22 +3285,22 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
@@ -3260,19 +3309,19 @@
         <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="AS13" t="s" s="2">
         <v>82</v>
@@ -3280,10 +3329,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3291,32 +3340,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3341,29 +3388,31 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Y14" s="2"/>
-      <c r="Z14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
@@ -3372,13 +3421,13 @@
         <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>82</v>
@@ -3387,64 +3436,66 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="AS14" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3453,7 +3504,7 @@
         <v>82</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>82</v>
@@ -3468,29 +3519,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -3502,10 +3555,10 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>82</v>
@@ -3517,16 +3570,16 @@
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>206</v>
+        <v>137</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AS15" t="s" s="2">
         <v>82</v>
@@ -3534,46 +3587,46 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3597,11 +3650,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3619,7 +3674,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -3643,19 +3698,19 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>82</v>
@@ -3663,14 +3718,12 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>82</v>
       </c>
@@ -3685,16 +3738,16 @@
         <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>197</v>
@@ -3711,7 +3764,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -3726,46 +3779,44 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI17" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -3774,7 +3825,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>204</v>
@@ -3794,10 +3845,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3811,25 +3862,25 @@
         <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3855,13 +3906,11 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -3879,7 +3928,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
@@ -3888,13 +3937,13 @@
         <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
@@ -3903,41 +3952,41 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AS18" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>94</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>95</v>
@@ -3946,21 +3995,21 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -3984,37 +4033,35 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -4023,71 +4070,73 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="AS19" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4098,7 +4147,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4113,13 +4162,11 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4137,7 +4184,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4152,7 +4199,7 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
@@ -4164,35 +4211,37 @@
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AS20" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>94</v>
@@ -4204,21 +4253,21 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4227,7 +4276,7 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>82</v>
@@ -4242,13 +4291,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4266,13 +4315,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4281,7 +4330,7 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
@@ -4290,19 +4339,19 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4310,10 +4359,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4333,19 +4382,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4371,13 +4420,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4395,7 +4444,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4419,38 +4468,38 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>94</v>
@@ -4465,18 +4514,18 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>273</v>
+        <v>195</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4500,29 +4549,31 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4537,43 +4588,41 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="AS23" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4582,10 +4631,10 @@
         <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
@@ -4594,16 +4643,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>284</v>
+        <v>195</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4629,13 +4678,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4653,13 +4702,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -4668,7 +4717,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -4677,38 +4726,38 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AS24" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>94</v>
@@ -4720,21 +4769,21 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4770,32 +4819,34 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
@@ -4804,19 +4855,19 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AS25" t="s" s="2">
         <v>82</v>
@@ -4824,14 +4875,12 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4843,25 +4892,25 @@
         <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4911,7 +4960,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -4920,34 +4969,34 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AS26" t="s" s="2">
         <v>82</v>
@@ -4981,15 +5030,17 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5026,16 +5077,14 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>296</v>
@@ -5053,7 +5102,7 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5062,19 +5111,19 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AS27" t="s" s="2">
         <v>82</v>
@@ -5082,12 +5131,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5099,7 +5150,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5108,15 +5159,17 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>304</v>
+        <v>172</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5165,7 +5218,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5180,7 +5233,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -5189,19 +5242,19 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AS28" t="s" s="2">
         <v>82</v>
@@ -5226,16 +5279,16 @@
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>310</v>
@@ -5243,7 +5296,9 @@
       <c r="M29" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5280,16 +5335,14 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>309</v>
@@ -5301,7 +5354,7 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>106</v>
@@ -5322,13 +5375,13 @@
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AS29" t="s" s="2">
         <v>82</v>
@@ -5336,12 +5389,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5350,10 +5405,10 @@
         <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5362,15 +5417,17 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>316</v>
+        <v>172</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5419,43 +5476,43 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS30" t="s" s="2">
         <v>82</v>
@@ -5463,10 +5520,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5480,22 +5537,22 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>322</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5546,7 +5603,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -5558,10 +5615,10 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
@@ -5576,13 +5633,13 @@
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AS31" t="s" s="2">
         <v>82</v>
@@ -5590,21 +5647,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5613,10 +5670,10 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>327</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>328</v>
@@ -5624,9 +5681,7 @@
       <c r="M32" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5675,43 +5730,43 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AR32" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>82</v>
@@ -5719,33 +5774,33 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>327</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>333</v>
@@ -5753,12 +5808,8 @@
       <c r="M33" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5806,43 +5857,43 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AQ33" t="s" s="2">
-        <v>137</v>
+        <v>336</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AS33" t="s" s="2">
         <v>82</v>
@@ -5850,10 +5901,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5864,7 +5915,7 @@
         <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5876,13 +5927,13 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>339</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5909,13 +5960,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5933,19 +5984,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>342</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -5960,13 +6011,13 @@
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>239</v>
+        <v>343</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -5977,10 +6028,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5991,7 +6042,7 @@
         <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6003,13 +6054,13 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>345</v>
+        <v>155</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>346</v>
+        <v>156</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6060,19 +6111,19 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>157</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6093,7 +6144,7 @@
         <v>82</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>347</v>
+        <v>158</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6104,21 +6155,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6130,15 +6181,17 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6163,13 +6216,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6187,19 +6240,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>162</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6220,7 +6273,7 @@
         <v>82</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>353</v>
+        <v>158</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6231,14 +6284,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6251,24 +6304,26 @@
         <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6316,7 +6371,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6328,7 +6383,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>358</v>
+        <v>145</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6349,7 +6404,7 @@
         <v>82</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6360,10 +6415,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6386,13 +6441,13 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>322</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6419,13 +6474,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6443,7 +6498,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6452,10 +6507,10 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6470,13 +6525,13 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>326</v>
+        <v>263</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
@@ -6494,7 +6549,7 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6513,17 +6568,15 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>139</v>
+        <v>362</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6572,7 +6625,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -6581,10 +6634,10 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6605,7 +6658,7 @@
         <v>82</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>326</v>
+        <v>365</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>82</v>
@@ -6616,46 +6669,42 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6679,13 +6728,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6703,19 +6752,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6736,7 +6785,7 @@
         <v>82</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>137</v>
+        <v>371</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>82</v>
@@ -6747,10 +6796,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6770,18 +6819,20 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>171</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6806,13 +6857,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6830,7 +6881,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -6839,10 +6890,10 @@
         <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>376</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6854,19 +6905,19 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>82</v>
@@ -6874,10 +6925,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6888,7 +6939,7 @@
         <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6897,16 +6948,16 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>155</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>156</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6957,19 +7008,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>157</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -6990,10 +7041,10 @@
         <v>82</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>347</v>
+        <v>158</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>82</v>
@@ -7001,14 +7052,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7027,15 +7078,17 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>377</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7084,7 +7137,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>162</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7096,38 +7149,550 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AR43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AR44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS43" t="s" s="2">
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AR45" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AR46" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AR47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS43">
+  <autoFilter ref="A1:AS47">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7137,7 +7702,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI42">
+  <conditionalFormatting sqref="A2:AI46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientCondition.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
